--- a/udt_tianfeng/data/params(GXHYTF).xlsx
+++ b/udt_tianfeng/data/params(GXHYTF).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14605"/>
+    <workbookView windowWidth="32065" windowHeight="14605"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="199">
   <si>
     <t>期货</t>
   </si>
@@ -614,6 +614,18 @@
   </si>
   <si>
     <t>br</t>
+  </si>
+  <si>
+    <t>铸造铝合金</t>
+  </si>
+  <si>
+    <t>SHFE</t>
+  </si>
+  <si>
+    <t>ad_o</t>
+  </si>
+  <si>
+    <t>ad</t>
   </si>
   <si>
     <t>原油</t>
@@ -1767,7 +1779,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr defaultColWidth="9.13513513513514" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="2" width="17.5585585585586" customWidth="1"/>
@@ -3690,24 +3702,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" ht="12.45" spans="1:12">
-      <c r="A52" s="6" t="s">
+    <row r="52" spans="1:12">
+      <c r="A52" t="s">
         <v>175</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" t="s">
         <v>176</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" t="s">
         <v>177</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" t="s">
         <v>178</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>28</v>
@@ -3719,17 +3731,17 @@
         <v>30</v>
       </c>
       <c r="J52">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="K52" s="9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L52" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="12.45" spans="1:12">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="7" t="s">
         <v>179</v>
       </c>
       <c r="B53" s="5" t="s">
@@ -3742,9 +3754,11 @@
         <v>182</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F53" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="G53" s="6" t="s">
         <v>28</v>
       </c>
@@ -3758,7 +3772,7 @@
         <v>100</v>
       </c>
       <c r="K53" s="9">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L53" s="1">
         <v>1</v>
@@ -3769,13 +3783,13 @@
         <v>183</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>70</v>
@@ -3801,17 +3815,17 @@
       </c>
     </row>
     <row r="55" ht="12.45" spans="1:12">
-      <c r="A55" s="7" t="s">
-        <v>186</v>
+      <c r="A55" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>70</v>
@@ -3838,27 +3852,29 @@
     </row>
     <row r="56" ht="12.45" spans="1:12">
       <c r="A56" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B56" s="6" t="s">
         <v>190</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>191</v>
+      <c r="D56" s="5" t="s">
+        <v>192</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H56" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I56" s="6" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J56">
         <v>100</v>
@@ -3878,13 +3894,13 @@
         <v>194</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6" t="s">
@@ -3901,6 +3917,40 @@
         <v>1</v>
       </c>
       <c r="L57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" ht="12.45" spans="1:12">
+      <c r="A58" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58">
+        <v>100</v>
+      </c>
+      <c r="K58" s="9">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1">
         <v>1</v>
       </c>
     </row>

--- a/udt_tianfeng/data/params(GXHYTF).xlsx
+++ b/udt_tianfeng/data/params(GXHYTF).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="227">
   <si>
     <t>期货</t>
   </si>
@@ -295,10 +295,22 @@
     <t>玉米淀粉</t>
   </si>
   <si>
+    <t>DCE</t>
+  </si>
+  <si>
     <t>cs_o</t>
   </si>
   <si>
     <t>cs</t>
+  </si>
+  <si>
+    <t>纯苯</t>
+  </si>
+  <si>
+    <t>bz_o</t>
+  </si>
+  <si>
+    <t>bz</t>
   </si>
   <si>
     <t>白糖</t>
@@ -747,6 +759,78 @@
   <si>
     <t>SZSE</t>
   </si>
+  <si>
+    <t>丙烯</t>
+  </si>
+  <si>
+    <t>PL_O</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>沥青</t>
+  </si>
+  <si>
+    <t>bu_o</t>
+  </si>
+  <si>
+    <t>bu</t>
+  </si>
+  <si>
+    <t>燃油</t>
+  </si>
+  <si>
+    <t>fu_o</t>
+  </si>
+  <si>
+    <t>fu</t>
+  </si>
+  <si>
+    <t>胶版纸</t>
+  </si>
+  <si>
+    <t>op_o</t>
+  </si>
+  <si>
+    <t>op</t>
+  </si>
+  <si>
+    <t>纸浆</t>
+  </si>
+  <si>
+    <t>sp_o</t>
+  </si>
+  <si>
+    <t>sp</t>
+  </si>
+  <si>
+    <t>动力煤</t>
+  </si>
+  <si>
+    <t>ZC_O</t>
+  </si>
+  <si>
+    <t>ZC</t>
+  </si>
+  <si>
+    <t>铂</t>
+  </si>
+  <si>
+    <t>pt_o</t>
+  </si>
+  <si>
+    <t>pt</t>
+  </si>
+  <si>
+    <t>钯</t>
+  </si>
+  <si>
+    <t>pd_o</t>
+  </si>
+  <si>
+    <t>pd</t>
+  </si>
 </sst>
 </file>
 
@@ -759,7 +843,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -781,6 +865,17 @@
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1254,152 +1349,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1418,12 +1513,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1779,7 +1879,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr defaultColWidth="9.13513513513514" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="2" width="17.5585585585586" customWidth="1"/>
@@ -1859,7 +1959,7 @@
       <c r="J2">
         <v>20</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="11">
         <v>1</v>
       </c>
       <c r="L2" s="1">
@@ -1893,7 +1993,7 @@
       <c r="J3">
         <v>20</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="11">
         <v>1</v>
       </c>
       <c r="L3" s="1">
@@ -1927,7 +2027,7 @@
       <c r="J4">
         <v>20</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="11">
         <v>1</v>
       </c>
       <c r="L4" s="1">
@@ -1965,7 +2065,7 @@
       <c r="J5">
         <v>1000</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="11">
         <v>1</v>
       </c>
       <c r="L5" s="1">
@@ -2003,7 +2103,7 @@
       <c r="J6">
         <v>2000</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="11">
         <v>1</v>
       </c>
       <c r="L6" s="1">
@@ -2041,7 +2141,7 @@
       <c r="J7">
         <v>1000</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="11">
         <v>1.5</v>
       </c>
       <c r="L7" s="1">
@@ -2079,7 +2179,7 @@
       <c r="J8">
         <v>1000</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="11">
         <v>1</v>
       </c>
       <c r="L8" s="1">
@@ -2117,7 +2217,7 @@
       <c r="J9">
         <v>1000</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="11">
         <v>1</v>
       </c>
       <c r="L9" s="1">
@@ -2155,7 +2255,7 @@
       <c r="J10">
         <v>1000</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="11">
         <v>1</v>
       </c>
       <c r="L10" s="1">
@@ -2163,7 +2263,7 @@
       </c>
     </row>
     <row r="11" ht="12.45" spans="1:12">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -2193,7 +2293,7 @@
       <c r="J11">
         <v>1000</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="11">
         <v>1</v>
       </c>
       <c r="L11" s="1">
@@ -2231,7 +2331,7 @@
       <c r="J12">
         <v>1000</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="11">
         <v>1</v>
       </c>
       <c r="L12" s="1">
@@ -2269,7 +2369,7 @@
       <c r="J13">
         <v>1000</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="11">
         <v>1</v>
       </c>
       <c r="L13" s="1">
@@ -2307,7 +2407,7 @@
       <c r="J14">
         <v>1000</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="11">
         <v>1</v>
       </c>
       <c r="L14" s="1">
@@ -2345,7 +2445,7 @@
       <c r="J15">
         <v>1000</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="11">
         <v>1</v>
       </c>
       <c r="L15" s="1">
@@ -2383,7 +2483,7 @@
       <c r="J16">
         <v>1000</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="11">
         <v>1</v>
       </c>
       <c r="L16" s="1">
@@ -2421,7 +2521,7 @@
       <c r="J17">
         <v>1000</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="11">
         <v>1</v>
       </c>
       <c r="L17" s="1">
@@ -2457,7 +2557,7 @@
       <c r="J18">
         <v>1000</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="11">
         <v>1</v>
       </c>
       <c r="L18" s="1">
@@ -2493,7 +2593,7 @@
       <c r="J19">
         <v>1000</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="11">
         <v>1</v>
       </c>
       <c r="L19" s="1">
@@ -2529,25 +2629,25 @@
       <c r="J20">
         <v>1000</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="11">
         <v>1</v>
       </c>
       <c r="L20" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="12.45" spans="1:12">
+    <row r="21" spans="1:12">
       <c r="A21" s="7" t="s">
         <v>77</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>26</v>
@@ -2567,19 +2667,19 @@
       <c r="J21">
         <v>1000</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="11">
         <v>1</v>
       </c>
       <c r="L21" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="12.45" spans="1:12">
-      <c r="A22" s="6" t="s">
-        <v>80</v>
+    <row r="22" spans="1:12">
+      <c r="A22" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>82</v>
@@ -2603,9 +2703,9 @@
         <v>30</v>
       </c>
       <c r="J22">
-        <v>100</v>
-      </c>
-      <c r="K22" s="9">
+        <v>1000</v>
+      </c>
+      <c r="K22" s="11">
         <v>1</v>
       </c>
       <c r="L22" s="1">
@@ -2617,13 +2717,13 @@
         <v>84</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>26</v>
@@ -2643,7 +2743,7 @@
       <c r="J23">
         <v>100</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="11">
         <v>1</v>
       </c>
       <c r="L23" s="1">
@@ -2652,16 +2752,16 @@
     </row>
     <row r="24" ht="12.45" spans="1:12">
       <c r="A24" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>26</v>
@@ -2681,7 +2781,7 @@
       <c r="J24">
         <v>100</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="11">
         <v>1</v>
       </c>
       <c r="L24" s="1">
@@ -2690,16 +2790,16 @@
     </row>
     <row r="25" ht="12.45" spans="1:12">
       <c r="A25" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>26</v>
@@ -2719,19 +2819,19 @@
       <c r="J25">
         <v>100</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="11">
         <v>1</v>
       </c>
       <c r="L25" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" ht="12.45" spans="1:12">
       <c r="A26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>95</v>
@@ -2757,11 +2857,11 @@
       <c r="J26">
         <v>100</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="11">
         <v>1</v>
       </c>
       <c r="L26" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2769,13 +2869,13 @@
         <v>97</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>26</v>
@@ -2795,30 +2895,32 @@
       <c r="J27">
         <v>100</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="11">
         <v>1</v>
       </c>
       <c r="L27" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" ht="12.45" spans="1:12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="G28" s="6" t="s">
         <v>28</v>
       </c>
@@ -2831,32 +2933,30 @@
       <c r="J28">
         <v>100</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="11">
         <v>1</v>
       </c>
       <c r="L28" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" ht="12.45" spans="1:12">
       <c r="A29" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>27</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F29" s="6"/>
       <c r="G29" s="6" t="s">
         <v>28</v>
       </c>
@@ -2869,25 +2969,25 @@
       <c r="J29">
         <v>100</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="11">
         <v>1</v>
       </c>
       <c r="L29" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="12.45" spans="1:12">
+    <row r="30" spans="1:12">
       <c r="A30" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>26</v>
@@ -2907,25 +3007,25 @@
       <c r="J30">
         <v>100</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="11">
         <v>1</v>
       </c>
       <c r="L30" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" ht="12.45" spans="1:12">
       <c r="A31" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>26</v>
@@ -2945,7 +3045,7 @@
       <c r="J31">
         <v>100</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="11">
         <v>1</v>
       </c>
       <c r="L31" s="1">
@@ -2954,16 +3054,16 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>26</v>
@@ -2983,30 +3083,32 @@
       <c r="J32">
         <v>100</v>
       </c>
-      <c r="K32" s="9">
-        <v>1.5</v>
+      <c r="K32" s="11">
+        <v>1</v>
       </c>
       <c r="L32" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="12.45" spans="1:12">
+    <row r="33" spans="1:12">
       <c r="A33" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F33" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="G33" s="6" t="s">
         <v>28</v>
       </c>
@@ -3019,8 +3121,8 @@
       <c r="J33">
         <v>100</v>
       </c>
-      <c r="K33" s="9">
-        <v>1</v>
+      <c r="K33" s="11">
+        <v>1.5</v>
       </c>
       <c r="L33" s="1">
         <v>1</v>
@@ -3028,16 +3130,16 @@
     </row>
     <row r="34" ht="12.45" spans="1:12">
       <c r="A34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>70</v>
@@ -3055,25 +3157,25 @@
       <c r="J34">
         <v>100</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="11">
         <v>1</v>
       </c>
       <c r="L34" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" ht="12.45" spans="1:12">
       <c r="A35" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>70</v>
@@ -3091,25 +3193,25 @@
       <c r="J35">
         <v>100</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="11">
         <v>1</v>
       </c>
       <c r="L35" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" ht="12.45" spans="1:12">
       <c r="A36" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B36" t="s">
-        <v>94</v>
+        <v>125</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>70</v>
@@ -3127,25 +3229,25 @@
       <c r="J36">
         <v>100</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="11">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="8" t="s">
-        <v>127</v>
+      <c r="A37" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" t="s">
-        <v>128</v>
-      </c>
-      <c r="D37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>129</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>70</v>
@@ -3163,7 +3265,7 @@
       <c r="J37">
         <v>100</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="11">
         <v>1</v>
       </c>
       <c r="L37" s="1">
@@ -3171,24 +3273,22 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="8" t="s">
-        <v>130</v>
+      <c r="A38" s="9" t="s">
+        <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>27</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F38" s="6"/>
       <c r="G38" s="6" t="s">
         <v>28</v>
       </c>
@@ -3201,25 +3301,25 @@
       <c r="J38">
         <v>100</v>
       </c>
-      <c r="K38" s="9">
-        <v>2</v>
+      <c r="K38" s="11">
+        <v>1</v>
       </c>
       <c r="L38" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="5" t="s">
+      <c r="A39" s="9" t="s">
         <v>134</v>
       </c>
+      <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" t="s">
+        <v>135</v>
+      </c>
       <c r="D39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>26</v>
@@ -3239,31 +3339,31 @@
       <c r="J39">
         <v>100</v>
       </c>
-      <c r="K39" s="9">
-        <v>1</v>
+      <c r="K39" s="11">
+        <v>2</v>
       </c>
       <c r="L39" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="40" ht="12.45" spans="1:12">
-      <c r="A40" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B40" s="6" t="s">
+    <row r="40" spans="1:12">
+      <c r="A40" s="7" t="s">
         <v>137</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" t="s">
         <v>139</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>28</v>
@@ -3277,7 +3377,7 @@
       <c r="J40">
         <v>100</v>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="11">
         <v>1</v>
       </c>
       <c r="L40" s="1">
@@ -3286,10 +3386,10 @@
     </row>
     <row r="41" ht="12.45" spans="1:12">
       <c r="A41" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>142</v>
@@ -3315,7 +3415,7 @@
       <c r="J41">
         <v>100</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="11">
         <v>1</v>
       </c>
       <c r="L41" s="1">
@@ -3327,7 +3427,7 @@
         <v>145</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>146</v>
@@ -3339,7 +3439,7 @@
         <v>26</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>28</v>
@@ -3353,7 +3453,7 @@
       <c r="J42">
         <v>100</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="11">
         <v>1</v>
       </c>
       <c r="L42" s="1">
@@ -3362,22 +3462,22 @@
     </row>
     <row r="43" ht="12.45" spans="1:12">
       <c r="A43" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>28</v>
@@ -3391,7 +3491,7 @@
       <c r="J43">
         <v>100</v>
       </c>
-      <c r="K43" s="9">
+      <c r="K43" s="11">
         <v>1</v>
       </c>
       <c r="L43" s="1">
@@ -3400,22 +3500,22 @@
     </row>
     <row r="44" ht="12.45" spans="1:12">
       <c r="A44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>28</v>
@@ -3429,7 +3529,7 @@
       <c r="J44">
         <v>100</v>
       </c>
-      <c r="K44" s="9">
+      <c r="K44" s="11">
         <v>1</v>
       </c>
       <c r="L44" s="1">
@@ -3438,22 +3538,22 @@
     </row>
     <row r="45" ht="12.45" spans="1:12">
       <c r="A45" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D45" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>156</v>
       </c>
+      <c r="D45" s="5" t="s">
+        <v>157</v>
+      </c>
       <c r="E45" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>28</v>
@@ -3467,7 +3567,7 @@
       <c r="J45">
         <v>100</v>
       </c>
-      <c r="K45" s="9">
+      <c r="K45" s="11">
         <v>1</v>
       </c>
       <c r="L45" s="1">
@@ -3475,23 +3575,23 @@
       </c>
     </row>
     <row r="46" ht="12.45" spans="1:12">
-      <c r="A46" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C46" s="5" t="s">
+      <c r="A46" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>159</v>
       </c>
+      <c r="D46" s="6" t="s">
+        <v>160</v>
+      </c>
       <c r="E46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>28</v>
@@ -3505,7 +3605,7 @@
       <c r="J46">
         <v>100</v>
       </c>
-      <c r="K46" s="9">
+      <c r="K46" s="11">
         <v>1</v>
       </c>
       <c r="L46" s="1">
@@ -3514,22 +3614,22 @@
     </row>
     <row r="47" ht="12.45" spans="1:12">
       <c r="A47" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>28</v>
@@ -3543,7 +3643,7 @@
       <c r="J47">
         <v>100</v>
       </c>
-      <c r="K47" s="9">
+      <c r="K47" s="11">
         <v>1</v>
       </c>
       <c r="L47" s="1">
@@ -3552,22 +3652,22 @@
     </row>
     <row r="48" ht="12.45" spans="1:12">
       <c r="A48" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>28</v>
@@ -3581,7 +3681,7 @@
       <c r="J48">
         <v>100</v>
       </c>
-      <c r="K48" s="9">
+      <c r="K48" s="11">
         <v>1</v>
       </c>
       <c r="L48" s="1">
@@ -3590,22 +3690,22 @@
     </row>
     <row r="49" ht="12.45" spans="1:12">
       <c r="A49" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>28</v>
@@ -3619,8 +3719,8 @@
       <c r="J49">
         <v>100</v>
       </c>
-      <c r="K49" s="9">
-        <v>1.5</v>
+      <c r="K49" s="11">
+        <v>1</v>
       </c>
       <c r="L49" s="1">
         <v>1</v>
@@ -3628,22 +3728,22 @@
     </row>
     <row r="50" ht="12.45" spans="1:12">
       <c r="A50" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>28</v>
@@ -3657,7 +3757,7 @@
       <c r="J50">
         <v>100</v>
       </c>
-      <c r="K50" s="9">
+      <c r="K50" s="11">
         <v>1.5</v>
       </c>
       <c r="L50" s="1">
@@ -3666,60 +3766,60 @@
     </row>
     <row r="51" ht="12.45" spans="1:12">
       <c r="A51" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>26</v>
       </c>
       <c r="F51" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J51">
+        <v>100</v>
+      </c>
+      <c r="K51" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="L51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" ht="12.45" spans="1:12">
+      <c r="A52" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F52" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J51">
-        <v>500</v>
-      </c>
-      <c r="K51" s="9">
-        <v>1</v>
-      </c>
-      <c r="L51" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" t="s">
-        <v>175</v>
-      </c>
-      <c r="B52" t="s">
-        <v>176</v>
-      </c>
-      <c r="C52" t="s">
-        <v>177</v>
-      </c>
-      <c r="D52" t="s">
-        <v>178</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>28</v>
@@ -3733,24 +3833,24 @@
       <c r="J52">
         <v>500</v>
       </c>
-      <c r="K52" s="9">
+      <c r="K52" s="11">
         <v>1</v>
       </c>
       <c r="L52" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="53" ht="12.45" spans="1:12">
-      <c r="A53" s="7" t="s">
+    <row r="53" spans="1:12">
+      <c r="A53" t="s">
         <v>179</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" t="s">
         <v>180</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" t="s">
         <v>181</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" t="s">
         <v>182</v>
       </c>
       <c r="E53" s="6" t="s">
@@ -3769,17 +3869,17 @@
         <v>30</v>
       </c>
       <c r="J53">
-        <v>100</v>
-      </c>
-      <c r="K53" s="9">
-        <v>1.5</v>
+        <v>500</v>
+      </c>
+      <c r="K53" s="11">
+        <v>1</v>
       </c>
       <c r="L53" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="54" ht="12.45" spans="1:12">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="7" t="s">
         <v>183</v>
       </c>
       <c r="B54" s="5" t="s">
@@ -3792,9 +3892,11 @@
         <v>186</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F54" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>148</v>
+      </c>
       <c r="G54" s="6" t="s">
         <v>28</v>
       </c>
@@ -3807,8 +3909,8 @@
       <c r="J54">
         <v>100</v>
       </c>
-      <c r="K54" s="9">
-        <v>1</v>
+      <c r="K54" s="11">
+        <v>1.5</v>
       </c>
       <c r="L54" s="1">
         <v>1</v>
@@ -3819,13 +3921,13 @@
         <v>187</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>70</v>
@@ -3841,9 +3943,9 @@
         <v>30</v>
       </c>
       <c r="J55">
-        <v>100</v>
-      </c>
-      <c r="K55" s="9">
+        <v>1000</v>
+      </c>
+      <c r="K55" s="11">
         <v>1</v>
       </c>
       <c r="L55" s="1">
@@ -3851,17 +3953,17 @@
       </c>
     </row>
     <row r="56" ht="12.45" spans="1:12">
-      <c r="A56" s="7" t="s">
-        <v>190</v>
+      <c r="A56" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>192</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>70</v>
@@ -3877,9 +3979,9 @@
         <v>30</v>
       </c>
       <c r="J56">
-        <v>100</v>
-      </c>
-      <c r="K56" s="9">
+        <v>500</v>
+      </c>
+      <c r="K56" s="11">
         <v>1</v>
       </c>
       <c r="L56" s="1">
@@ -3888,32 +3990,34 @@
     </row>
     <row r="57" ht="12.45" spans="1:12">
       <c r="A57" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B57" s="6" t="s">
         <v>194</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>195</v>
+      <c r="D57" s="5" t="s">
+        <v>196</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H57" s="6"/>
+        <v>28</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="I57" s="6" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J57">
-        <v>100</v>
-      </c>
-      <c r="K57" s="9">
+        <v>1000</v>
+      </c>
+      <c r="K57" s="11">
         <v>1</v>
       </c>
       <c r="L57" s="1">
@@ -3928,13 +4032,13 @@
         <v>198</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6" t="s">
@@ -3945,12 +4049,345 @@
         <v>17</v>
       </c>
       <c r="J58">
+        <v>50</v>
+      </c>
+      <c r="K58" s="11">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" ht="12.45" spans="1:12">
+      <c r="A59" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59">
+        <v>50</v>
+      </c>
+      <c r="K59" s="11">
+        <v>1</v>
+      </c>
+      <c r="L59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B60" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" t="s">
+        <v>204</v>
+      </c>
+      <c r="D60" t="s">
+        <v>205</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J60">
         <v>100</v>
       </c>
-      <c r="K58" s="9">
-        <v>1</v>
-      </c>
-      <c r="L58" s="1">
+      <c r="K60" s="11">
+        <v>1</v>
+      </c>
+      <c r="L60" s="1">
+        <v>1</v>
+      </c>
+      <c r="M60" s="10"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B61" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" t="s">
+        <v>207</v>
+      </c>
+      <c r="D61" t="s">
+        <v>208</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J61">
+        <v>100</v>
+      </c>
+      <c r="K61" s="11">
+        <v>1</v>
+      </c>
+      <c r="L61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="B62" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62" t="s">
+        <v>210</v>
+      </c>
+      <c r="D62" t="s">
+        <v>211</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J62">
+        <v>100</v>
+      </c>
+      <c r="K62" s="11">
+        <v>1</v>
+      </c>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B63" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" t="s">
+        <v>213</v>
+      </c>
+      <c r="D63" t="s">
+        <v>214</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J63">
+        <v>100</v>
+      </c>
+      <c r="K63" s="11">
+        <v>1</v>
+      </c>
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B64" t="s">
+        <v>180</v>
+      </c>
+      <c r="C64" t="s">
+        <v>216</v>
+      </c>
+      <c r="D64" t="s">
+        <v>217</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J64">
+        <v>100</v>
+      </c>
+      <c r="K64" s="11">
+        <v>1</v>
+      </c>
+      <c r="L64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B65" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" t="s">
+        <v>219</v>
+      </c>
+      <c r="D65" t="s">
+        <v>220</v>
+      </c>
+      <c r="E65" t="s">
+        <v>26</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J65">
+        <v>100</v>
+      </c>
+      <c r="K65" s="11">
+        <v>1</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" ht="12.45" spans="1:12">
+      <c r="A66" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" t="s">
+        <v>222</v>
+      </c>
+      <c r="D66" t="s">
+        <v>223</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J66">
+        <v>100</v>
+      </c>
+      <c r="K66" s="11">
+        <v>1</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" ht="13.7" spans="1:12">
+      <c r="A67" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J67">
+        <v>100</v>
+      </c>
+      <c r="K67" s="11">
+        <v>1</v>
+      </c>
+      <c r="L67" s="1">
         <v>1</v>
       </c>
     </row>
